--- a/inputs/restricciones.xlsx
+++ b/inputs/restricciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\git\Trabajos\programacion_academica\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9716D2-FB06-4863-91C1-AFA7B21EBC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16859478-5B9A-483C-B457-91CB1E9EE2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D202CC0-A9D2-45DA-8C5E-EE99A13988CB}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="102">
   <si>
     <t>Asignatura</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>31/07/2026 - 22/08/2026</t>
+  </si>
+  <si>
+    <t>SEMANA_INICIO</t>
   </si>
 </sst>
 </file>
@@ -1234,7 +1237,7 @@
         <v>4</v>
       </c>
       <c r="I12" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J12" s="13"/>
       <c r="K12" s="16">
@@ -1417,7 +1420,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39DA9563-36FC-4DCE-9A98-1BAFFA5C2DB7}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -1510,6 +1513,14 @@
       </c>
       <c r="B11" s="4">
         <v>46312</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" s="3">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
